--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/11 10:42:40</t>
+          <t>09/17 18:20:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>8974.36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/11 10:39:47</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>8860.76</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>8974.36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15189.87</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>15189.87</t>
+          <t>8974.36</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 18:20:33</t>
+          <t>09/18 10:24:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8974.36</t>
+          <t>6329.11</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/18 11:56:15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12820.51</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/18 10:24:21</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>50000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>6329.11</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6329.11</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19149.63</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6329.11</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19149.63</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 11:56:15</t>
+          <t>09/20 17:05:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12820.51</t>
+          <t>10322.58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,186 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/18 10:24:21</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>6329.11</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>80000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>10322.58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19149.63</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>19149.63</t>
+          <t>10322.58</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 17:05:11</t>
+          <t>09/22 13:49:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/22 13:49:28</t>
+          <t>09/28 23:32:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>aoe168188</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>45000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10322.58</t>
+          <t>5769.23</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 23:32:07</t>
+          <t>09/29 10:22:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>aoe168188</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>45000</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5769.23</t>
+          <t>20779.22</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/29 10:28:07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>160000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20779.22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20779.22</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.22</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/29 12:01:33</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>140000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18181.82</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/29 10:22:56</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20779.22</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>160000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20779.22</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20779</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.22</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18182.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38961.04</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>38960</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>18182.04</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 12:29:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/29 12:28:49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18181</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/29 10:28:07</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>20779</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38961.04</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38960</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>59739</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.04</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-20777.96</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 12:29:09</t>
+          <t>09/29 12:28:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,12 +271,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
+          <t>09/29 10:28:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -286,7 +286,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -295,86 +295,59 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>09/29 10:28:07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>38961.04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38961.04</t>
+          <t>38960</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>59739</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>-20777.96</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 12:01:33</t>
+          <t>09/30 18:34:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>16835.44</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/29 10:22:56</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20779.22</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/29 12:28:49</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18181</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/29 10:28:07</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>133000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16835.44</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>300000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>38961.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>38960</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.04</t>
+          <t>16835.44</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/30 19:01:32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16835</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>133000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>133000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16835.44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16835</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>16835.44</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.44</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/30 19:09:04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16835</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/30 19:01:32</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>16835</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>133000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>133000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16835</t>
+          <t>16835.44</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>33670</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.44</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>-16834.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -202,7 +202,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/30 19:09:04</t>
+          <t>09/30 19:01:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -217,7 +217,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -226,86 +226,59 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>09/30 19:01:32</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>16835</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>133000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>16835.44</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>16835</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>33670</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>-16834.56</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 18:34:09</t>
+          <t>10/07 21:08:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>10389.61</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/30 19:01:32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16835</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>80000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>10389.61</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16835.44</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16835</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.44</t>
+          <t>10389.61</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/07 21:28:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>80000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>80000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10389.61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10389</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10389.61</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.61</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 21:08:01</t>
+          <t>10/09 16:44:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>5203.25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/07 21:28:34</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10389</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>41626</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>5203.25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10389.61</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10389</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.61</t>
+          <t>5203.25</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 16:44:02</t>
+          <t>10/11 16:30:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41626</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5203.25</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/11 16:30:06</t>
+          <t>10/12 14:15:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>6410.26</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 14:15:32</t>
+          <t>10/13 13:22:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/13 14:02:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12987.01</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 13:22:12</t>
+          <t>10/16 12:33:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>39473.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/13 14:02:36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12987</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>39473.68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12987</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.01</t>
+          <t>39473.68</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/16 12:34:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39473.68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>39473.68</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19473.68</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/16 12:56:10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19473</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/16 12:34:05</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>39473.68</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>39473</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>19473.68</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.68</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/16 12:33:53</t>
+          <t>10/17 09:24:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39473.68</t>
+          <t>6410.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>CS_006</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/16 12:56:10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>19473</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/16 12:34:05</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6410.26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>39473.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>39473</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.68</t>
+          <t>6410.26</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/17 10:20:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6410.26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6410.26</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.26</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/17 09:24:46</t>
+          <t>10/19 11:12:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/17 10:20:01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6410</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6410.26</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6410</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.26</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/19 11:36:12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12987.01</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/19 14:36:42</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>107700</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>13134.15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/19 11:12:13</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>100000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>12987.01</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/19 11:36:12</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>12987</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>207700</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>26121.16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.01</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13134.16</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10/19 15:38:07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13134</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/19 11:36:12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>12987</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>207700</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26121.16</t>
+          <t>207700</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>26121.16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>26121</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>13134.16</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.16</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/19 14:36:42</t>
+          <t>10/20 13:50:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107700</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13134.15</t>
+          <t>20779.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/19 11:12:13</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12987.01</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/19 15:38:07</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>13134</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/19 11:36:12</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12987</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>160000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20779.22</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>207700</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>26121.16</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>26121</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.16</t>
+          <t>20779.22</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,183 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/20 14:16:14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12987.01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/20 13:50:02</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>160000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>20779.22</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-    </row>
+          <t>10/20 14:16:30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>20779.22</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>33766.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20779.22</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13766.23</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>10/20 15:07:22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13766</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>10/20 14:16:30</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>260000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33766.23</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>33766.23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>33766</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>13766.23</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.23</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/20 14:16:14</t>
+          <t>10/21 14:53:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>17073.17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/20 13:50:02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>160000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20779.22</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/20 15:07:22</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>13766</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/20 14:16:30</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20000</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>140000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17073.17</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>260000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>33766.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>33766</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.23</t>
+          <t>17073.17</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/21 15:34:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17073</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>140000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>140000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17073.17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17073</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17073.17</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.17</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/21 14:53:16</t>
+          <t>10/26 10:21:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>27500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/21 15:34:08</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>17073</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>27500</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17073.17</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17073</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.17</t>
+          <t>27500</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/26 10:40:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>27500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>27500</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/26 11:54:43</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>145000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18831.17</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/26 10:21:46</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>220000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>27500</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/26 10:40:36</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>27500</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>365000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>46331.17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>27500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18831.17</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/26 11:54:43</t>
+          <t>10/27 13:29:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18831.17</t>
+          <t>12987.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/26 10:21:46</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>220000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>27500</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/26 10:40:36</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>27500</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>365000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>46331.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>27500</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>18831.17</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/27 14:03:24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12987.01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12987</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12987.01</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 13:29:58</t>
+          <t>10/28 13:19:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>15853.66</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS_006</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -202,12 +202,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/27 14:03:24</t>
+          <t>10/28 14:30:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -242,7 +242,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>130000</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12987.01</t>
+          <t>15853.66</t>
         </is>
       </c>
     </row>
@@ -266,7 +266,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>15853</t>
         </is>
       </c>
     </row>
@@ -278,7 +278,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.66</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>10/28 15:04:59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>136000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>17662.34</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CS_006</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>10/28 13:19:13</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>130000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>15853.66</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/28 14:30:51</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>15853</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>130000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15853.66</t>
+          <t>266000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>33516</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15853</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.66</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17663</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/28 15:04:59</t>
+          <t>10/31 11:18:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>136000</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17662.34</t>
+          <t>19231.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -114,213 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>10/28 13:19:13</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15853.66</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/28 14:30:51</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>15853</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CS_006</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>157700</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19231.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33516</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>15853</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>17663</t>
+          <t>19231.71</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
+++ b/bills/huixinjiqiren/-5570663976/2f51b32dbd10be530766037e3aafda2a0cabe66a37e0289074ce7a7a9f114a35/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/31 11:19:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>157700</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19231.71</t>
+          <t>157700</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19231.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>19231.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18543.71</t>
         </is>
       </c>
     </row>
